--- a/data/crop_estimates.xlsx
+++ b/data/crop_estimates.xlsx
@@ -406,7 +406,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -462,7 +462,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8074,7 +8074,7 @@
         <v>30</v>
       </c>
       <c r="C314" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D314">
         <v>25.122</v>
@@ -8838,7 +8838,7 @@
         <v>60</v>
       </c>
       <c r="C345" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D345">
         <v>2.8849999999999998</v>
@@ -8916,7 +8916,7 @@
         <v>63</v>
       </c>
       <c r="C348" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D348">
         <v>3.9249999999999998</v>
@@ -8942,7 +8942,7 @@
         <v>65</v>
       </c>
       <c r="C349" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D349">
         <v>3.069</v>
